--- a/source/_static/技术参数.xlsx
+++ b/source/_static/技术参数.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\001---jaka\V01-iM-D\source\_static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4468187E-5CC2-44CA-9344-6C4A9F0341C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7393EA58-E528-42A9-A1A3-862F287588CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -343,7 +343,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>DI*7；DO*7；RS485*2；USB*1；RJ45*2；HDMI*1</t>
+    <t>DI*8；DO*8；RS485*2；USB*1；RJ45*2；HDMI*1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
